--- a/template_with_headers.xlsx
+++ b/template_with_headers.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
   <si>
     <t>#{orders.site_name}</t>
   </si>
@@ -19,10 +19,10 @@
     <t>#{operation_categories.name}</t>
   </si>
   <si>
-    <t>番</t>
-  </si>
-  <si>
-    <t>符</t>
+    <t>番号</t>
+  </si>
+  <si>
+    <t>符号</t>
   </si>
   <si>
     <t>主筋</t>
@@ -55,19 +55,7 @@
     <t>#{blueprints.image}</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
     <t>EOB</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>C2</t>
   </si>
 </sst>
 </file>
@@ -522,14 +510,15 @@
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3"/>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
       <c r="P3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -541,14 +530,15 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4"/>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
       <c r="P4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -560,8 +550,15 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
       <c r="P5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -573,8 +570,15 @@
       <c r="F6"/>
       <c r="G6"/>
       <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
       <c r="P6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -586,8 +590,15 @@
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
       <c r="P7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -599,8 +610,15 @@
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
       <c r="P8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -613,7 +631,7 @@
       <c r="G9"/>
       <c r="H9"/>
       <c r="P9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -626,7 +644,7 @@
       <c r="G10"/>
       <c r="H10"/>
       <c r="P10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -639,7 +657,7 @@
       <c r="G11"/>
       <c r="H11"/>
       <c r="P11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -652,7 +670,7 @@
       <c r="G12"/>
       <c r="H12"/>
       <c r="P12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -665,7 +683,7 @@
       <c r="G13"/>
       <c r="H13"/>
       <c r="P13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -678,7 +696,7 @@
       <c r="G14"/>
       <c r="H14"/>
       <c r="P14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -691,7 +709,7 @@
       <c r="G15"/>
       <c r="H15"/>
       <c r="P15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -704,7 +722,7 @@
       <c r="G16"/>
       <c r="H16"/>
       <c r="P16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -717,7 +735,7 @@
       <c r="G17"/>
       <c r="H17"/>
       <c r="P17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -730,7 +748,7 @@
       <c r="G18"/>
       <c r="H18"/>
       <c r="P18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -743,7 +761,7 @@
       <c r="G19"/>
       <c r="H19"/>
       <c r="P19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -756,7 +774,7 @@
       <c r="G20"/>
       <c r="H20"/>
       <c r="P20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -769,7 +787,7 @@
       <c r="G21"/>
       <c r="H21"/>
       <c r="P21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -782,7 +800,7 @@
       <c r="G22"/>
       <c r="H22"/>
       <c r="P22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -795,7 +813,7 @@
       <c r="G23"/>
       <c r="H23"/>
       <c r="P23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -808,7 +826,7 @@
       <c r="G24"/>
       <c r="H24"/>
       <c r="P24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -821,7 +839,7 @@
       <c r="G25"/>
       <c r="H25"/>
       <c r="P25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -834,7 +852,7 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="P26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -847,7 +865,7 @@
       <c r="G27"/>
       <c r="H27"/>
       <c r="P27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -860,7 +878,7 @@
       <c r="G28"/>
       <c r="H28"/>
       <c r="P28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -873,7 +891,7 @@
       <c r="G29"/>
       <c r="H29"/>
       <c r="P29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -886,7 +904,7 @@
       <c r="G30"/>
       <c r="H30"/>
       <c r="P30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -899,7 +917,7 @@
       <c r="G31"/>
       <c r="H31"/>
       <c r="P31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -913,16 +931,21 @@
       <c r="H32"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="I1:I8"/>
+    <mergeCell ref="J1:J8"/>
     <mergeCell ref="A3:H32"/>
+    <mergeCell ref="K2:K8"/>
+    <mergeCell ref="L2:L8"/>
+    <mergeCell ref="M2:M8"/>
+    <mergeCell ref="N2:N8"/>
+    <mergeCell ref="O2:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
